--- a/backend/fms_core/tests/invalid_templates/Sample_Rename_v5_6_0_no_sample.xlsx
+++ b/backend/fms_core/tests/invalid_templates/Sample_Rename_v5_6_0_no_sample.xlsx
@@ -128,7 +128,7 @@
     <t xml:space="preserve">Index Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Old Sample Name</t>
+    <t xml:space="preserve">Old Sample Name or Pool Name</t>
   </si>
   <si>
     <t xml:space="preserve">Old Sample Alias</t>
